--- a/artfynd/A 3340-2022 artfynd.xlsx
+++ b/artfynd/A 3340-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3340-2022 artfynd.xlsx
+++ b/artfynd/A 3340-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98719273</v>
+        <v>98721412</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>373154.0106835028</v>
+        <v>373154</v>
       </c>
       <c r="R2" t="n">
-        <v>6624794.972424261</v>
+        <v>6624795</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -751,19 +746,9 @@
           <t>2022-02-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98721412</v>
+        <v>98719273</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373154.0106835028</v>
+        <v>373154</v>
       </c>
       <c r="R3" t="n">
-        <v>6624794.972424261</v>
+        <v>6624795</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -867,19 +847,9 @@
           <t>2022-02-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
